--- a/光伏配储项目/电价数据/2026/锦霖站.xlsx
+++ b/光伏配储项目/电价数据/2026/锦霖站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.36105</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38455</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.83823</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.39262</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.41726</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.3742799999999999</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.40993</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.31465</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.39095</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.26449</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.37314</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.36722</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.42213</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.39806</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.08445999999999999</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.18245</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.28732</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.26363</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.26803</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.25293</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.4089</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.87595</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.36736</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.50814</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.52171</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.2984</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.59965</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.58439</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.75379</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.16905</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39858</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.57371</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43747</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44468</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.67628</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.9196599999999999</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.5303099999999999</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.23691</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.38107</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.1351</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.13396</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.34465</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.45327</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.47369</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.73268</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.7868200000000001</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.23171</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.97341</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.93135</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.81747</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7816900000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.52758</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.49914</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.47988</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.42547</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.43631</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.75161</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.93106</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.00953</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5258700000000001</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.54274</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.53435</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.53452</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.5149</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.41428</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.49422</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38903</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38407</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.29554</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.30212</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.19415</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.15634</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.21094</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.38874</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38919</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.38207</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.4838</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.35413</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.3919</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30096</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.36817</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.53315</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.53425</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.72719</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7062</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.93245</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.42221</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.40471</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.40279</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.3777</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.46537</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.87281</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.58141</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.4709100000000001</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.4088</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.42616</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.71256</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.44083</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.40293</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.62922</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.8144600000000001</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.87517</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.23105</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.63731</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.17429</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.90395</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.26662</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.15721</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.34129</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.08444</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.14176</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.69467</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.03531</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.94652</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.02104</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.8911</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.16153</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.96763</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.46056</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.9245599999999999</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.97433</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45929</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43663</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.45334</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38301</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33613</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5337499999999999</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.51062</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.5154099999999999</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.46414</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42835</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.39441</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.44716</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.46568</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37971</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.41048</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37748</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37764</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.36378</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.37021</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38344</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.40317</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.49826</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45691</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.45675</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.4057</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.09114</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.13215</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.26382</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.41025</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.0494</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.99997</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.78895</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.7723099999999999</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.99607</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.98702</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.9519</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.9585900000000001</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.02075</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.96094</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.9132</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.88836</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.06105</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.56214</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.64107</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.8340700000000001</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.85349</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.71539</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.77666</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.54325</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.9527</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.46861</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39732</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45283</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.52076</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.53037</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.6088600000000001</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.66018</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.68745</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.69467</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.3799</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.63993</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.6919299999999999</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.47449</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50956</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.6834199999999999</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.84802</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.83282</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.9703200000000001</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.48813</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.70427</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.45655</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.5406599999999999</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.64608</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.87081</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.59753</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.9929199999999999</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.7896599999999999</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.65046</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.60854</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.74648</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.44486</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.46613</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40232</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34374</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.53899</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.5188700000000001</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.45604</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.40092</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40113</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37568</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39737</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.4678</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36885</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.37325</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36582</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36734</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35354</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35829</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39567</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.3988</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38394</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39991</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42351</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44299</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.4348</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.5194099999999999</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.6555800000000001</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.43396</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.4487</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.28142</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.26356</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.63501</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.3877</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.37439</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.42924</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.66204</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.5781799999999999</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.47965</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.41644</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.51266</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.71185</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.50641</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.54803</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45077</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.48392</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40659</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.51102</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.6239600000000001</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.7299500000000001</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.5218400000000001</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.64915</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.55722</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.5280900000000001</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50302</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.47498</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.44992</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.43652</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.38628</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31406</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.34427</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37764</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31302</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31327</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30389</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.29643</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31522</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.2844100000000001</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.37436</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13982</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.01597</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.36297</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.38876</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.5341900000000001</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.5357799999999999</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.53975</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.43676</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.44195</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.30206</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.28094</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.27127</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.14149</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.56808</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.5194099999999999</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26336</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30025</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30465</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.35191</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.43823</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.4094</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.3092</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.38385</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.24771</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.27659</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.19209</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.20537</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.19293</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.27092</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.15794</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.28966</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.12073</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.22338</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31011</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.29793</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.14423</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.22879</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.18628</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.16191</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.28029</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.13893</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.29823</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.22786</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.2517</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.16767</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.25551</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10045</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04215</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04484</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.009210000000000001</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20466</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04849000000000001</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27314</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.1244</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05881</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05701</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.3111</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.29539</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.35376</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29727</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38308</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.43336</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.4651</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.40855</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7861699999999999</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9141900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88748</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18706</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87013</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.6409900000000001</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5673400000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49313</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44992</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20697</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45451</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42161</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39107</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37618</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38102</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.3898</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32221</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32248</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.30306</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.42644</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.29498</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5500499999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.58693</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.90426</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.48113</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.25893</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.40621</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.56188</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.28079</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.85458</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.29035</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.28558</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.2886</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.25763</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.6139199999999999</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.45356</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31503</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.38322</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.51483</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.38446</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29078</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29593</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29025</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.14709</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.25105</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.24942</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.26599</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.24676</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.27066</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.28021</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.30319</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30108</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.29337</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.28346</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.28307</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.2767</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.27641</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.27496</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.27624</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.28492</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.26997</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.3164</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.89354</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.29923</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.29663</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.29161</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.30478</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.29706</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.30161</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.2806</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.29449</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.29124</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.28988</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.27344</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.28265</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.29289</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.27552</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.2864</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.28495</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.28338</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.27983</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.2881</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.29604</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.28677</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.28729</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.29763</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.29724</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30072</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.3088399999999999</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.2073</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30416</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.14465</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.17842</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.18779</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.23991</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.21011</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.2989</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.30311</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.38481</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.40217</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.19064</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.32449</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2736</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.31109</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.29817</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.31671</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.29588</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.29917</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.30667</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.29243</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.29019</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.45102</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44394</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.30167</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.25085</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.21385</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.87451</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.56845</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.23366</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7247</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.83614</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.67355</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.16437</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.18721</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45553</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.51107</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.45363</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.36922</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41913</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40226</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.29955</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.39864</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42626</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.27933</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43079</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.26076</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.26058</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.37936</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.40973</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.26291</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.39797</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.3762200000000001</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.26943</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.26678</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.38192</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.26447</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.47562</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.13681</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.27831</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.2768</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.28618</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29433</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.28725</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.39961</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.26213</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.29993</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15034</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27169</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.28082</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.02167</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.27637</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.27271</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.29363</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29874</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28758</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.3047</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30021</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.29321</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.30717</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.27173</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.34179</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.32066</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.27728</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.42833</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.5324</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.30659</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.27805</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.29616</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.29488</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.28624</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.26392</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.28414</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.25302</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.24488</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.24493</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.23862</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.12787</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.16016</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.15352</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.15227</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.15115</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.11715</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.22279</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.24529</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.24276</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.29478</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.12437</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.12327</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.29128</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.28597</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.16788</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.13881</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.17963</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.15643</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.14044</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.25764</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.22751</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.26368</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.12174</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.28474</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.12209</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.19045</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29022</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.28016</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.13354</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25735</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.2729</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.26692</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.26571</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.27708</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.27718</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.28732</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.26383</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.25698</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.28849</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.28509</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.29209</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.28394</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.27612</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.27521</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.26024</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.27159</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.27775</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.27072</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.27632</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.26997</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.26151</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.26653</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.26747</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.4091</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.37316</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.3641</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.2665</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.26928</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.22583</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.26525</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.27765</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.2581</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.27286</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.28127</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.28068</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.28167</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.28174</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.28316</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.2852</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.29219</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.29219</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.28789</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.28843</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.2783</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.28298</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.28328</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.28617</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.28351</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.28326</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.2839100000000001</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.28326</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.28853</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.26581</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.27788</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.28183</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.28565</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.29179</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.27915</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.29199</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.28671</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.2933</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.29814</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.27852</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.26861</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28212</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.17322</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.23972</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.06708</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.06377000000000001</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28025</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.08942</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.19398</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30096</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.29922</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.29242</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29085</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.18597</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.24564</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.1758</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.27343</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.27466</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.25647</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30219</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31082</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.27252</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.36573</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.45133</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.27584</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.30326</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.3137200000000001</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31236</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.30762</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.26546</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.29266</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.29317</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.29392</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.29206</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.29388</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.24766</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33397</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.26685</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.29449</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.29211</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.26753</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.27648</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.27067</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.28006</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.28571</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.28713</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.30949</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.28375</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.28384</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3057</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30116</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.28238</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.30248</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.28302</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.28444</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.28256</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.26706</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.29128</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.30171</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.28432</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.29187</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.40847</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.17392</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.41642</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.69313</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.38166</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.50042</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.47287</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.37089</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.44061</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.50395</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.37751</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.43005</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.5625800000000001</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27396</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.27762</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.40066</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.21609</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.35572</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.71338</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.45419</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.38621</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.42644</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.40574</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.54704</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.41323</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.39563</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.43825</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.36396</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.42336</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.39506</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.43339</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.37113</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.65064</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.46556</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.41783</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.46912</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.43861</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.70565</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.17187</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.25904</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.27836</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.47408</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22198</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.30483</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.29429</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.25728</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.2685</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.17631</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.25279</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.37614</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.26917</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.26473</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.26313</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.25722</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.16274</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.15635</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.26004</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.26089</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.26063</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.26072</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.26106</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.26106</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.15779</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.28791</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.15551</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.11149</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.21429</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.28273</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.28591</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.24647</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.15525</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.16124</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.19429</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.16591</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.12171</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.11485</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.18322</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.21497</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.2792</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.29962</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.28151</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31151</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.29041</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.26631</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.28511</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.2864</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.2808</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.28424</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.24731</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.28399</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.28971</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.27869</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.29077</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.29403</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.29875</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.28623</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.27653</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.27605</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.26135</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.2713</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.27653</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.20584</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.28304</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.35191</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.28085</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.29927</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.28738</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.29398</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.30551</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.29411</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.28737</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.2134</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.27271</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.24052</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.30904</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.26747</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.25193</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.26531</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.25919</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.26546</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.19749</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.25317</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.18484</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.12925</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.20619</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.31246</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.28092</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.31309</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.31406</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.26386</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.27448</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.26976</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.2581</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.30228</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.30274</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.27231</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.26199</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.28708</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.26938</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.26743</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.27268</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.25666</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.30774</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.27145</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.27505</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.27443</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.29903</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.26572</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.26079</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.26818</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.28115</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.25981</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.27188</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.26104</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.28273</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.29242</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30118</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31426</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.29679</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.30822</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30081</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.29965</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37017</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.29275</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.30045</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.3132799999999999</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.31317</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.31457</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.31556</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.31427</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.30472</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.29879</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.30983</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.30541</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.39916</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.62627</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.43763</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.16488</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.29925</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.28496</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.37388</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.30054</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.29955</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.26279</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.29154</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.31392</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30258</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.30559</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.29482</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.21559</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>-0.04883</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31237</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.10166</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.00941</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.11828</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.09745999999999999</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.23134</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.19318</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.26778</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.22136</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.20022</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.18859</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.26211</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.39913</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.36955</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.28559</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.31159</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.41085</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.47521</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.65637</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.61317</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6575800000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.27145</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.81674</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.29724</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.27654</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.29622</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.49703</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40641</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.43852</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.30667</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.27717</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.28926</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.29152</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.30595</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.30302</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.29079</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.28666</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.26857</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.29649</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.29461</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.29299</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.29546</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.30174</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.28383</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.29009</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.28358</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.28947</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.25963</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.27962</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.28578</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.26907</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.24063</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.25974</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.2305</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.26196</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.27745</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.26477</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.27871</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.4367</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.39475</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.40505</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.44312</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.48062</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.5180800000000001</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5571699999999999</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.39731</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.30047</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.29673</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.36277</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.42103</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.67171</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40175</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.8131699999999999</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.3905</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.30288</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.19069</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.30042</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31003</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.00349</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.28221</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.38957</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.04025</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.04893</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.29837</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.28823</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.27952</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.27602</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.27241</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.26725</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.22874</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.19076</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.27568</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.22404</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.23564</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.25458</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.25432</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.22807</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7430399999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.5927</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6352000000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.28609</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.2779700000000001</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.27693</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.2834</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.27815</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.29883</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.27355</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.29511</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.2914</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.28443</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.39721</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.38715</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.28372</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.29176</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.21976</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.25965</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.26309</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.29164</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.28884</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.29809</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.28796</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.25217</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.26503</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.24857</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.25654</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.27301</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.2946</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.35405</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.36221</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.30458</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.37885</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.39882</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.38724</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.37651</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.39951</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.38868</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.41402</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.42584</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.40338</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.28149</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.19172</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.09064</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.2829100000000001</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.28867</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.29454</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.30369</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.36651</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.28966</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.19601</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.40768</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38023</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.12194</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.1971</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.19129</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.21536</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.25456</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.25313</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.2074</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.25143</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.2781</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.26523</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.1422</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.27919</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.14023</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.1541</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.14751</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.18835</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.15752</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.26082</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.23877</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.24022</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.19301</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.2364</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.18159</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.12143</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.23864</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.12175</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.16387</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.12046</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.11321</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.11672</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.16022</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.11493</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.11707</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.11921</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.12135</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.12996</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.14818</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.10728</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.27599</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>-0.02574</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.1656</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.01005</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29293</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.2211</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.22946</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.25051</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.24965</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.03122</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.2833</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.27427</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.2859</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.29547</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.29659</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.22162</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.24742</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.27232</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.28191</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.28848</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.28144</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.23749</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.26554</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.25026</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.24687</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.18085</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.21045</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.18852</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.21259</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.24279</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.2743</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.23419</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.22667</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.13229</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.13839</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.2338</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.12374</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.26254</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.12599</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.21221</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.20578</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.26787</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.26733</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.26377</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.26707</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.25637</v>
+      </c>
+      <c r="H136" t="n">
+        <v>-0.03181</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.14998</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.14749</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.18178</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.20586</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.19649</v>
+      </c>
+      <c r="P136" t="n">
+        <v>-0.02125</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.1762</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.1504</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.29917</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.23902</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.01624</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.01201</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00045</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.16307</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02215</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.0133</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04299</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04090999999999999</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04862</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02937</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04291</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00448</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28079</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04928</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03497</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.00605</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03487</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.21112</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.27151</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29647</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.2842</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.27982</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.29204</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.28995</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.29122</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.30188</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.2982</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.28763</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28194</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30156</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29253</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.30804</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.29462</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.29973</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29466</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28191</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29429</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.25403</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.24333</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.24946</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.27799</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.25081</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.27739</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.25107</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.25952</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.13257</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.12975</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.1335</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.13131</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.12794</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.11864</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.40945</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.15391</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.26089</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.20418</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.18662</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85262</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.86358</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.08318</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.23617</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.28113</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.40721</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.6974</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.30887</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29812</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00311</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00227</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.07042</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30314</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30894</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25451</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47608</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31398</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.5323099999999999</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.48595</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.28705</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.36176</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.71392</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.95675</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.30832</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.57989</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.37269</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.8166599999999999</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.81489</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.81916</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.9175599999999999</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.29137</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.31071</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34274</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.29457</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.30306</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.2774</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.2588</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.4664</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.27025</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.26438</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.24188</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.23876</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.15198</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.24162</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.23423</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.22855</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.1906</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.20833</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.17399</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.17005</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.12737</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.12967</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.1142</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.14442</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.20038</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.27779</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.2379</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.21212</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.2195</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.2363</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.26266</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.27766</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.28833</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.31857</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.2631</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30648</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31427</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30881</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25886</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31151</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30268</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30247</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.3838</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.3925</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.28892</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.21927</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.29538</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.28029</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.29567</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.29705</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.29295</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.28556</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.30242</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.29337</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.28333</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.27629</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.27818</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33834</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.31418</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.30711</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.30179</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.30164</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.30541</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.30546</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.3017</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.2922</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.29207</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.28392</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.2882</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.29582</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.29207</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.30072</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.29651</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.30144</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.30866</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.27551</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.30149</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.27581</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.5521200000000001</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.25609</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.42729</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.30917</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.28565</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.29799</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.32666</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.35633</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.45468</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.42291</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47656</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.05264</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.82038</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.7942</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.39895</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.38566</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.53807</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.63547</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.8688400000000001</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.38832</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.52788</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.30857</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.41538</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.31703</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.29403</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.19109</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.30894</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.29723</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.30628</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.38618</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.30707</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.30832</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.30908</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.30582</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.29533</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.29405</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.28765</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.28296</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.28001</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.29117</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.28981</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.28885</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39092</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43453</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.35591</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29263</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37827</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.36493</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39458</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.37548</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5102599999999999</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.50354</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.05336</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.8016599999999999</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.5279299999999999</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.67996</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.4674</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5578500000000001</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49568</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.42215</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.6579700000000001</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.6125499999999999</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.01858</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.83628</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.7112000000000001</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5666599999999999</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.39804</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.31095</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27908</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.29871</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.27141</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.28311</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.27696</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.28949</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.28063</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.28749</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.28997</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.29165</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.27726</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.27769</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31371</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.27057</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.30873</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.27488</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.26529</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.29293</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.30589</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.29184</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.31707</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.36312</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.25608</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.41591</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.51097</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.32266</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19692</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43471</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.47491</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.30845</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.28716</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.41283</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35216</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36095</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.4953</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.44081</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.5295800000000001</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.4321</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.42424</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.39053</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.45175</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.54015</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.38514</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.47259</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.40508</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.41064</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.31413</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.6721</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.44354</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.41606</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.40457</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.3541</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.3410899999999999</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.32797</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31348</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.30582</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.37693</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.29326</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.25204</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.38169</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.47101</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.29995</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32384</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35352</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.46355</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.47676</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.45188</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.46002</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.48942</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.37468</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38811</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.40231</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36381</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.36727</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.41458</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.49926</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.41002</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36377</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.40378</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.3883</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33105</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34847</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.28679</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37226</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.30558</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.32607</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30271</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17621</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30423</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29602</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14587</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19882</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14816</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28686</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04885</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12239</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22724</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26014</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14207</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14633</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28338</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18612</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22701</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27712</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.16239</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36479</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.17339</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20544</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.16417</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.3083399999999999</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.34283</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.40766</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.46088</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.40339</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.60229</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.42288</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.40055</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.45147</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.40511</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33609</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.49739</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.4533</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.49628</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.48798</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37665</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.46463</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.45626</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.46985</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.48045</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40963</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39273</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.36356</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38352</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38398</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.36048</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36342</v>
       </c>
     </row>
   </sheetData>
